--- a/paper_data_package/timepix_paper_data_package.xlsx
+++ b/paper_data_package/timepix_paper_data_package.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_index" sheetId="1" r:id="R0ecff27c242f4d29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_main" sheetId="2" r:id="R33ae6e1d08fd486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_runs" sheetId="3" r:id="Rc66a3df7396d4604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_per_class" sheetId="4" r:id="R3284e23a43214303"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_errors" sheetId="5" r:id="Rd7971269a5284800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_modality" sheetId="6" r:id="Rd95d48dcaa9e4325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_features" sheetId="7" r:id="R649e583fccf0423d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06a_hc_models" sheetId="8" r:id="R30ca910d7fde4f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06b_hc_import" sheetId="9" r:id="R01dbd7b3dbf6439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06c_hc_cnn" sheetId="10" r:id="R25f9b53fd6534439"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_loss" sheetId="11" r:id="Rb5c52f30ec324915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_excluded" sheetId="12" r:id="R53a44ba7d8ea4303"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_missing" sheetId="13" r:id="Rf35070768f164219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_decisions" sheetId="14" r:id="R019f8b5988b04923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_index" sheetId="1" r:id="Rf430dc3e37da4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_main" sheetId="2" r:id="R560cad3421544fad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_runs" sheetId="3" r:id="R6b59b4b823bd401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_per_class" sheetId="4" r:id="R0cb957b78a6a4965"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_errors" sheetId="5" r:id="Rdb9432ba93564ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_modality" sheetId="6" r:id="R5e46a1980d0c4126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_features" sheetId="7" r:id="R5223471aaebd4f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06a_hc_models" sheetId="8" r:id="Rab59a142cc344051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06b_hc_import" sheetId="9" r:id="R991d4caab463415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06c_hc_cnn" sheetId="10" r:id="Rd19fcb4a54734262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_loss" sheetId="11" r:id="R1b10cbc277a848f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_excluded" sheetId="12" r:id="R99122ffbc9f844f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_missing" sheetId="13" r:id="Rcf208dc0804348d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_decisions" sheetId="14" r:id="R147acbe140424ac3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5085,9 +5085,15 @@
       <x:c r="T17" t="n">
         <x:v>0.5796890184645287</x:v>
       </x:c>
-      <x:c r="U17"/>
-      <x:c r="V17"/>
-      <x:c r="W17"/>
+      <x:c r="U17" t="n">
+        <x:v>0.9552150178957939</x:v>
+      </x:c>
+      <x:c r="V17" t="n">
+        <x:v>0.9164272687030246</x:v>
+      </x:c>
+      <x:c r="W17" t="n">
+        <x:v>0.0005830903790087463</x:v>
+      </x:c>
       <x:c r="X17" t="n">
         <x:v>0.940868045441305</x:v>
       </x:c>
@@ -5097,8 +5103,12 @@
       <x:c r="Z17" t="n">
         <x:v>0.9575670197022168</x:v>
       </x:c>
-      <x:c r="AA17"/>
-      <x:c r="AB17"/>
+      <x:c r="AA17" t="n">
+        <x:v>0.91863879621825</x:v>
+      </x:c>
+      <x:c r="AB17" t="n">
+        <x:v>0.0005825808330905913</x:v>
+      </x:c>
       <x:c r="AC17" t="str">
         <x:v>outputs/b1_proton_c7_resnet18_tot_best_patience8_3seed_runs.csv</x:v>
       </x:c>
@@ -5157,9 +5167,15 @@
       <x:c r="T18" t="n">
         <x:v>0.5597667638483965</x:v>
       </x:c>
-      <x:c r="U18"/>
-      <x:c r="V18"/>
-      <x:c r="W18"/>
+      <x:c r="U18" t="n">
+        <x:v>0.9563269487717777</x:v>
+      </x:c>
+      <x:c r="V18" t="n">
+        <x:v>0.9188773211938727</x:v>
+      </x:c>
+      <x:c r="W18" t="n">
+        <x:v>0.0002915451895043732</x:v>
+      </x:c>
       <x:c r="X18" t="n">
         <x:v>0.9432954655791824</x:v>
       </x:c>
@@ -5169,8 +5185,12 @@
       <x:c r="Z18" t="n">
         <x:v>0.9586565739590428</x:v>
       </x:c>
-      <x:c r="AA18"/>
-      <x:c r="AB18"/>
+      <x:c r="AA18" t="n">
+        <x:v>0.9220042879812039</x:v>
+      </x:c>
+      <x:c r="AB18" t="n">
+        <x:v>0.0005825808330905913</x:v>
+      </x:c>
       <x:c r="AC18" t="str">
         <x:v>outputs/b1_proton_c7_resnet18_tot_best_patience8_3seed_runs.csv</x:v>
       </x:c>
@@ -5229,9 +5249,15 @@
       <x:c r="T19" t="n">
         <x:v>0.8882410106899903</x:v>
       </x:c>
-      <x:c r="U19"/>
-      <x:c r="V19"/>
-      <x:c r="W19"/>
+      <x:c r="U19" t="n">
+        <x:v>0.9351107796115335</x:v>
+      </x:c>
+      <x:c r="V19" t="n">
+        <x:v>0.8726892880241257</x:v>
+      </x:c>
+      <x:c r="W19" t="n">
+        <x:v>0.0012633624878522838</x:v>
+      </x:c>
       <x:c r="X19" t="n">
         <x:v>0.9136809398970774</x:v>
       </x:c>
@@ -5241,8 +5267,12 @@
       <x:c r="Z19" t="n">
         <x:v>0.9388233945398462</x:v>
       </x:c>
-      <x:c r="AA19"/>
-      <x:c r="AB19"/>
+      <x:c r="AA19" t="n">
+        <x:v>0.8795365875687089</x:v>
+      </x:c>
+      <x:c r="AB19" t="n">
+        <x:v>0.0009709680551509856</x:v>
+      </x:c>
       <x:c r="AC19" t="str">
         <x:v>outputs/b1_proton_c7_resnet18_tot_best_patience8_3seed_runs.csv</x:v>
       </x:c>
@@ -8527,7 +8557,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>val_high_angle_macro_f1_mean</x:v>
+        <x:v>val_far_error_rate_abs_ge_20_mean</x:v>
       </x:c>
       <x:c r="C43" t="n">
         <x:v>12</x:v>
@@ -8539,16 +8569,16 @@
         <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="F43" t="str">
-        <x:v>partially_recoverable</x:v>
+        <x:v>source_missing</x:v>
       </x:c>
       <x:c r="G43" t="str">
         <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
       </x:c>
       <x:c r="H43" t="str">
-        <x:v>A4b 可从 by_class 派生 high-angle F1；若仍为空通常说明该行没有 by_class 对应项。</x:v>
+        <x:v>A4b 后处理汇总未保存混淆矩阵或逐样本预测，不能稳定派生 far-error。</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>检查具体 strategy 是否在 by_class 中。</x:v>
+        <x:v>如论文需要该指标，应扩展 A4b 脚本保存预测或混淆矩阵后重算。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -8556,7 +8586,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>val_high_angle_macro_f1_std</x:v>
+        <x:v>val_far_error_rate_abs_ge_20_std</x:v>
       </x:c>
       <x:c r="C44" t="n">
         <x:v>12</x:v>
@@ -8568,16 +8598,16 @@
         <x:v>0.6666666666666666</x:v>
       </x:c>
       <x:c r="F44" t="str">
-        <x:v>partially_recoverable</x:v>
+        <x:v>source_missing</x:v>
       </x:c>
       <x:c r="G44" t="str">
         <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
       </x:c>
       <x:c r="H44" t="str">
-        <x:v>A4b 可从 by_class 派生 high-angle F1；若仍为空通常说明该行没有 by_class 对应项。</x:v>
+        <x:v>A4b 后处理汇总未保存混淆矩阵或逐样本预测，不能稳定派生 far-error。</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>检查具体 strategy 是否在 by_class 中。</x:v>
+        <x:v>如论文需要该指标，应扩展 A4b 脚本保存预测或混淆矩阵后重算。</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -8585,7 +8615,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>val_far_error_rate_abs_ge_20_mean</x:v>
+        <x:v>test_far_error_rate_abs_ge_20_mean</x:v>
       </x:c>
       <x:c r="C45" t="n">
         <x:v>12</x:v>
@@ -8614,7 +8644,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>val_far_error_rate_abs_ge_20_std</x:v>
+        <x:v>test_far_error_rate_abs_ge_20_std</x:v>
       </x:c>
       <x:c r="C46" t="n">
         <x:v>12</x:v>
@@ -8643,28 +8673,28 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>test_high_angle_macro_f1_mean</x:v>
+        <x:v>expert_gate_freeze_experts</x:v>
       </x:c>
       <x:c r="C47" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D47" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E47" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8888888888888888</x:v>
       </x:c>
       <x:c r="F47" t="str">
-        <x:v>partially_recoverable</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G47" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
+        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
       </x:c>
       <x:c r="H47" t="str">
-        <x:v>A4b 可从 by_class 派生 high-angle F1；若仍为空通常说明该行没有 by_class 对应项。</x:v>
+        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>检查具体 strategy 是否在 by_class 中。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -8672,28 +8702,28 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>test_high_angle_macro_f1_std</x:v>
+        <x:v>val_gate_primary_mean_mean</x:v>
       </x:c>
       <x:c r="C48" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D48" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E48" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8888888888888888</x:v>
       </x:c>
       <x:c r="F48" t="str">
-        <x:v>partially_recoverable</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G48" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
+        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
       </x:c>
       <x:c r="H48" t="str">
-        <x:v>A4b 可从 by_class 派生 high-angle F1；若仍为空通常说明该行没有 by_class 对应项。</x:v>
+        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>检查具体 strategy 是否在 by_class 中。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -8701,28 +8731,28 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>test_far_error_rate_abs_ge_20_mean</x:v>
+        <x:v>val_gate_primary_mean_std</x:v>
       </x:c>
       <x:c r="C49" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D49" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E49" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8888888888888888</x:v>
       </x:c>
       <x:c r="F49" t="str">
-        <x:v>source_missing</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G49" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
+        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
       </x:c>
       <x:c r="H49" t="str">
-        <x:v>A4b 后处理汇总未保存混淆矩阵或逐样本预测，不能稳定派生 far-error。</x:v>
+        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>如论文需要该指标，应扩展 A4b 脚本保存预测或混淆矩阵后重算。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -8730,28 +8760,28 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>test_far_error_rate_abs_ge_20_std</x:v>
+        <x:v>test_gate_primary_mean_mean</x:v>
       </x:c>
       <x:c r="C50" t="n">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D50" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E50" t="n">
-        <x:v>0.6666666666666666</x:v>
+        <x:v>0.8888888888888888</x:v>
       </x:c>
       <x:c r="F50" t="str">
-        <x:v>source_missing</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G50" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate</x:v>
+        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
       </x:c>
       <x:c r="H50" t="str">
-        <x:v>A4b 后处理汇总未保存混淆矩阵或逐样本预测，不能稳定派生 far-error。</x:v>
+        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>如论文需要该指标，应扩展 A4b 脚本保存预测或混淆矩阵后重算。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -8759,7 +8789,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>expert_gate_freeze_experts</x:v>
+        <x:v>test_gate_primary_mean_std</x:v>
       </x:c>
       <x:c r="C51" t="n">
         <x:v>16</x:v>
@@ -8788,7 +8818,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>val_gate_primary_mean_mean</x:v>
+        <x:v>val_gate_candidate_mean_mean</x:v>
       </x:c>
       <x:c r="C52" t="n">
         <x:v>16</x:v>
@@ -8817,7 +8847,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>val_gate_primary_mean_std</x:v>
+        <x:v>val_gate_candidate_mean_std</x:v>
       </x:c>
       <x:c r="C53" t="n">
         <x:v>16</x:v>
@@ -8846,7 +8876,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>test_gate_primary_mean_mean</x:v>
+        <x:v>test_gate_candidate_mean_mean</x:v>
       </x:c>
       <x:c r="C54" t="n">
         <x:v>16</x:v>
@@ -8875,7 +8905,7 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>test_gate_primary_mean_std</x:v>
+        <x:v>test_gate_candidate_mean_std</x:v>
       </x:c>
       <x:c r="C55" t="n">
         <x:v>16</x:v>
@@ -8904,25 +8934,25 @@
         <x:v>05_modality_and_gate_diagnostics.csv</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>val_gate_candidate_mean_mean</x:v>
+        <x:v>handcrafted_features</x:v>
       </x:c>
       <x:c r="C56" t="n">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D56" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E56" t="n">
-        <x:v>0.8888888888888888</x:v>
+        <x:v>0.9444444444444444</x:v>
       </x:c>
       <x:c r="F56" t="str">
         <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G56" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
+        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
       </x:c>
       <x:c r="H56" t="str">
-        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
+        <x:v>该实验没有启用手工特征。</x:v>
       </x:c>
       <x:c r="I56" t="str">
         <x:v>保持空值或在展示时标为 NA。</x:v>
@@ -8930,350 +8960,350 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B57" t="str">
-        <x:v>val_gate_candidate_mean_std</x:v>
+        <x:v>split</x:v>
       </x:c>
       <x:c r="C57" t="n">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D57" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E57" t="n">
-        <x:v>0.8888888888888888</x:v>
+        <x:v>0.8787878787878788</x:v>
       </x:c>
       <x:c r="F57" t="str">
-        <x:v>not_applicable</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G57" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H57" t="str">
-        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B58" t="str">
-        <x:v>test_gate_candidate_mean_mean</x:v>
+        <x:v>accuracy</x:v>
       </x:c>
       <x:c r="C58" t="n">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D58" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E58" t="n">
-        <x:v>0.8888888888888888</x:v>
+        <x:v>0.8787878787878788</x:v>
       </x:c>
       <x:c r="F58" t="str">
-        <x:v>not_applicable</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G58" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H58" t="str">
-        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B59" t="str">
-        <x:v>test_gate_candidate_mean_std</x:v>
+        <x:v>macro_f1</x:v>
       </x:c>
       <x:c r="C59" t="n">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D59" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E59" t="n">
-        <x:v>0.8888888888888888</x:v>
+        <x:v>0.8787878787878788</x:v>
       </x:c>
       <x:c r="F59" t="str">
-        <x:v>not_applicable</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G59" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A7</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H59" t="str">
-        <x:v>该字段只对特定 gate/FiLM/selector 方法存在。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>handcrafted_features</x:v>
+        <x:v>mae_argmax</x:v>
       </x:c>
       <x:c r="C60" t="n">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D60" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E60" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.8787878787878788</x:v>
       </x:c>
       <x:c r="F60" t="str">
-        <x:v>not_applicable</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G60" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H60" t="str">
-        <x:v>该实验没有启用手工特征。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>val_confusion_45_50_mean</x:v>
+        <x:v>handcrafted_features</x:v>
       </x:c>
       <x:c r="C61" t="n">
-        <x:v>17</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D61" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E61" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.12121212121212122</x:v>
       </x:c>
       <x:c r="F61" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G61" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H61" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>val_confusion_45_50_std</x:v>
+        <x:v>val_baseline_accuracy</x:v>
       </x:c>
       <x:c r="C62" t="n">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D62" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E62" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.7575757575757576</x:v>
       </x:c>
       <x:c r="F62" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G62" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H62" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>test_confusion_45_50_mean</x:v>
+        <x:v>importance_mean</x:v>
       </x:c>
       <x:c r="C63" t="n">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D63" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E63" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.7575757575757576</x:v>
       </x:c>
       <x:c r="F63" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G63" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H63" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>test_confusion_45_50_std</x:v>
+        <x:v>importance_std</x:v>
       </x:c>
       <x:c r="C64" t="n">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D64" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E64" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.7575757575757576</x:v>
       </x:c>
       <x:c r="F64" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G64" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
       </x:c>
       <x:c r="H64" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>val_confusion_60_70_mean</x:v>
+        <x:v>model</x:v>
       </x:c>
       <x:c r="C65" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D65" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E65" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F65" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G65" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H65" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>val_confusion_60_70_std</x:v>
+        <x:v>loss</x:v>
       </x:c>
       <x:c r="C66" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D66" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E66" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F66" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G66" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H66" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>test_confusion_60_70_mean</x:v>
+        <x:v>label_encoding</x:v>
       </x:c>
       <x:c r="C67" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D67" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E67" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F67" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G67" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H67" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>05_modality_and_gate_diagnostics.csv</x:v>
+        <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>test_confusion_60_70_std</x:v>
+        <x:v>seed</x:v>
       </x:c>
       <x:c r="C68" t="n">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D68" t="n">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E68" t="n">
-        <x:v>0.9444444444444444</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F68" t="str">
-        <x:v>needs_review</x:v>
+        <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G68" t="str">
-        <x:v>A4b-5;A4b-6;A4b-candidate;A4c-1-3;A4c-4</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H68" t="str">
-        <x:v>未被规则自动归类。</x:v>
+        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>人工抽查源文件。</x:v>
+        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -9281,22 +9311,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>split</x:v>
+        <x:v>handcrafted_source_modalities</x:v>
       </x:c>
       <x:c r="C69" t="n">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D69" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E69" t="n">
-        <x:v>0.8787878787878788</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F69" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G69" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H69" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9310,22 +9340,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>accuracy</x:v>
+        <x:v>comparison_role</x:v>
       </x:c>
       <x:c r="C70" t="n">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D70" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E70" t="n">
-        <x:v>0.8787878787878788</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F70" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G70" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H70" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9339,22 +9369,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>macro_f1</x:v>
+        <x:v>val_accuracy</x:v>
       </x:c>
       <x:c r="C71" t="n">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D71" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E71" t="n">
-        <x:v>0.8787878787878788</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F71" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H71" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9368,22 +9398,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>mae_argmax</x:v>
+        <x:v>val_mae_argmax</x:v>
       </x:c>
       <x:c r="C72" t="n">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D72" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E72" t="n">
-        <x:v>0.8787878787878788</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F72" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G72" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H72" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9397,16 +9427,16 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>handcrafted_features</x:v>
+        <x:v>val_macro_f1</x:v>
       </x:c>
       <x:c r="C73" t="n">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D73" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E73" t="n">
-        <x:v>0.12121212121212122</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F73" t="str">
         <x:v>heterogeneous_combined_table</x:v>
@@ -9426,22 +9456,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>val_baseline_accuracy</x:v>
+        <x:v>test_accuracy</x:v>
       </x:c>
       <x:c r="C74" t="n">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D74" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E74" t="n">
-        <x:v>0.7575757575757576</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F74" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G74" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H74" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9455,22 +9485,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>importance_mean</x:v>
+        <x:v>test_mae_argmax</x:v>
       </x:c>
       <x:c r="C75" t="n">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D75" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E75" t="n">
-        <x:v>0.7575757575757576</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F75" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G75" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H75" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9484,22 +9514,22 @@
         <x:v>06_handcrafted_feature_results.csv</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>importance_std</x:v>
+        <x:v>test_macro_f1</x:v>
       </x:c>
       <x:c r="C76" t="n">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D76" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E76" t="n">
-        <x:v>0.7575757575757576</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="F76" t="str">
         <x:v>heterogeneous_combined_table</x:v>
       </x:c>
       <x:c r="G76" t="str">
-        <x:v>A5a;A5b;A5c;A5d;A7;B2a;B2b</x:v>
+        <x:v>A5a</x:v>
       </x:c>
       <x:c r="H76" t="str">
         <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
@@ -9510,640 +9540,147 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
+        <x:v>07_loss_strategy_results.csv</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>model</x:v>
+        <x:v>gaussian_sigma</x:v>
       </x:c>
       <x:c r="C77" t="n">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D77" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E77" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.8181818181818182</x:v>
       </x:c>
       <x:c r="F77" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>A5a</x:v>
+        <x:v>A2-best;A6a;A6b;B1-best;B3a;B3b-main;B3b-optional</x:v>
       </x:c>
       <x:c r="H77" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
+        <x:v>该字段只对对应损失函数存在。</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
+        <x:v>07_loss_strategy_results.csv</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>loss</x:v>
+        <x:v>expected_mae_weight</x:v>
       </x:c>
       <x:c r="C78" t="n">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D78" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E78" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.7272727272727273</x:v>
       </x:c>
       <x:c r="F78" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G78" t="str">
-        <x:v>A5a</x:v>
+        <x:v>A2-best;A6a;A6b;B1-best;B3a;B3b-optional</x:v>
       </x:c>
       <x:c r="H78" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
+        <x:v>该字段只对对应损失函数存在。</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
+        <x:v>07_loss_strategy_results.csv</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>label_encoding</x:v>
+        <x:v>emd_weight</x:v>
       </x:c>
       <x:c r="C79" t="n">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D79" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E79" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="F79" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>A5a</x:v>
+        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
       </x:c>
       <x:c r="H79" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
+        <x:v>该字段只对对应损失函数存在。</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
+        <x:v>07_loss_strategy_results.csv</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>seed</x:v>
+        <x:v>emd_p</x:v>
       </x:c>
       <x:c r="C80" t="n">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D80" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E80" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="F80" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G80" t="str">
-        <x:v>A5a</x:v>
+        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
       </x:c>
       <x:c r="H80" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
+        <x:v>该字段只对对应损失函数存在。</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
+        <x:v>保持空值或在展示时标为 NA。</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
+        <x:v>07_loss_strategy_results.csv</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>handcrafted_source_modalities</x:v>
+        <x:v>emd_angle_weighted</x:v>
       </x:c>
       <x:c r="C81" t="n">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D81" t="n">
         <x:v>33</x:v>
       </x:c>
       <x:c r="E81" t="n">
-        <x:v>0.36363636363636365</x:v>
+        <x:v>0.6363636363636364</x:v>
       </x:c>
       <x:c r="F81" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
+        <x:v>not_applicable</x:v>
       </x:c>
       <x:c r="G81" t="str">
-        <x:v>A5a</x:v>
+        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
       </x:c>
       <x:c r="H81" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
+        <x:v>该字段只对对应损失函数存在。</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B82" t="str">
-        <x:v>comparison_role</x:v>
-      </x:c>
-      <x:c r="C82" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D82" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E82" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F82" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G82" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H82" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I82" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B83" t="str">
-        <x:v>val_accuracy</x:v>
-      </x:c>
-      <x:c r="C83" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D83" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E83" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F83" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G83" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H83" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I83" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B84" t="str">
-        <x:v>val_mae_argmax</x:v>
-      </x:c>
-      <x:c r="C84" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D84" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E84" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F84" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G84" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H84" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I84" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B85" t="str">
-        <x:v>val_macro_f1</x:v>
-      </x:c>
-      <x:c r="C85" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D85" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E85" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F85" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G85" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H85" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I85" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B86" t="str">
-        <x:v>test_accuracy</x:v>
-      </x:c>
-      <x:c r="C86" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D86" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E86" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F86" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G86" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H86" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I86" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B87" t="str">
-        <x:v>test_mae_argmax</x:v>
-      </x:c>
-      <x:c r="C87" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D87" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E87" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F87" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G87" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H87" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I87" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" t="str">
-        <x:v>06_handcrafted_feature_results.csv</x:v>
-      </x:c>
-      <x:c r="B88" t="str">
-        <x:v>test_macro_f1</x:v>
-      </x:c>
-      <x:c r="C88" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D88" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E88" t="n">
-        <x:v>0.36363636363636365</x:v>
-      </x:c>
-      <x:c r="F88" t="str">
-        <x:v>heterogeneous_combined_table</x:v>
-      </x:c>
-      <x:c r="G88" t="str">
-        <x:v>A5a</x:v>
-      </x:c>
-      <x:c r="H88" t="str">
-        <x:v>该表合并了经典模型指标、特征重要性和 CNN 融合三种行类型。</x:v>
-      </x:c>
-      <x:c r="I88" t="str">
-        <x:v>论文分析优先使用 06a/06b/06c 拆分表。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B89" t="str">
-        <x:v>gaussian_sigma</x:v>
-      </x:c>
-      <x:c r="C89" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D89" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E89" t="n">
-        <x:v>0.8181818181818182</x:v>
-      </x:c>
-      <x:c r="F89" t="str">
-        <x:v>not_applicable</x:v>
-      </x:c>
-      <x:c r="G89" t="str">
-        <x:v>A2-best;A6a;A6b;B1-best;B3a;B3b-main;B3b-optional</x:v>
-      </x:c>
-      <x:c r="H89" t="str">
-        <x:v>该字段只对对应损失函数存在。</x:v>
-      </x:c>
-      <x:c r="I89" t="str">
         <x:v>保持空值或在展示时标为 NA。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B90" t="str">
-        <x:v>expected_mae_weight</x:v>
-      </x:c>
-      <x:c r="C90" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D90" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E90" t="n">
-        <x:v>0.7272727272727273</x:v>
-      </x:c>
-      <x:c r="F90" t="str">
-        <x:v>not_applicable</x:v>
-      </x:c>
-      <x:c r="G90" t="str">
-        <x:v>A2-best;A6a;A6b;B1-best;B3a;B3b-optional</x:v>
-      </x:c>
-      <x:c r="H90" t="str">
-        <x:v>该字段只对对应损失函数存在。</x:v>
-      </x:c>
-      <x:c r="I90" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B91" t="str">
-        <x:v>emd_weight</x:v>
-      </x:c>
-      <x:c r="C91" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D91" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E91" t="n">
-        <x:v>0.6363636363636364</x:v>
-      </x:c>
-      <x:c r="F91" t="str">
-        <x:v>not_applicable</x:v>
-      </x:c>
-      <x:c r="G91" t="str">
-        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
-      </x:c>
-      <x:c r="H91" t="str">
-        <x:v>该字段只对对应损失函数存在。</x:v>
-      </x:c>
-      <x:c r="I91" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B92" t="str">
-        <x:v>emd_p</x:v>
-      </x:c>
-      <x:c r="C92" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D92" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E92" t="n">
-        <x:v>0.6363636363636364</x:v>
-      </x:c>
-      <x:c r="F92" t="str">
-        <x:v>not_applicable</x:v>
-      </x:c>
-      <x:c r="G92" t="str">
-        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
-      </x:c>
-      <x:c r="H92" t="str">
-        <x:v>该字段只对对应损失函数存在。</x:v>
-      </x:c>
-      <x:c r="I92" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B93" t="str">
-        <x:v>emd_angle_weighted</x:v>
-      </x:c>
-      <x:c r="C93" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D93" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E93" t="n">
-        <x:v>0.6363636363636364</x:v>
-      </x:c>
-      <x:c r="F93" t="str">
-        <x:v>not_applicable</x:v>
-      </x:c>
-      <x:c r="G93" t="str">
-        <x:v>A2-best;A6a;B1-best;B3a;B3b-main</x:v>
-      </x:c>
-      <x:c r="H93" t="str">
-        <x:v>该字段只对对应损失函数存在。</x:v>
-      </x:c>
-      <x:c r="I93" t="str">
-        <x:v>保持空值或在展示时标为 NA。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B94" t="str">
-        <x:v>val_macro_f1</x:v>
-      </x:c>
-      <x:c r="C94" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D94" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E94" t="n">
-        <x:v>0.09090909090909091</x:v>
-      </x:c>
-      <x:c r="F94" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="G94" t="str">
-        <x:v>B1-best</x:v>
-      </x:c>
-      <x:c r="H94" t="str">
-        <x:v>未被规则自动归类。</x:v>
-      </x:c>
-      <x:c r="I94" t="str">
-        <x:v>人工抽查源文件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B95" t="str">
-        <x:v>val_high_angle_macro_f1</x:v>
-      </x:c>
-      <x:c r="C95" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D95" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E95" t="n">
-        <x:v>0.09090909090909091</x:v>
-      </x:c>
-      <x:c r="F95" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="G95" t="str">
-        <x:v>B1-best</x:v>
-      </x:c>
-      <x:c r="H95" t="str">
-        <x:v>未被规则自动归类。</x:v>
-      </x:c>
-      <x:c r="I95" t="str">
-        <x:v>人工抽查源文件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B96" t="str">
-        <x:v>val_far_error_rate_abs_ge_20</x:v>
-      </x:c>
-      <x:c r="C96" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D96" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E96" t="n">
-        <x:v>0.09090909090909091</x:v>
-      </x:c>
-      <x:c r="F96" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="G96" t="str">
-        <x:v>B1-best</x:v>
-      </x:c>
-      <x:c r="H96" t="str">
-        <x:v>未被规则自动归类。</x:v>
-      </x:c>
-      <x:c r="I96" t="str">
-        <x:v>人工抽查源文件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B97" t="str">
-        <x:v>test_high_angle_macro_f1</x:v>
-      </x:c>
-      <x:c r="C97" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D97" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E97" t="n">
-        <x:v>0.09090909090909091</x:v>
-      </x:c>
-      <x:c r="F97" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="G97" t="str">
-        <x:v>B1-best</x:v>
-      </x:c>
-      <x:c r="H97" t="str">
-        <x:v>未被规则自动归类。</x:v>
-      </x:c>
-      <x:c r="I97" t="str">
-        <x:v>人工抽查源文件。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" t="str">
-        <x:v>07_loss_strategy_results.csv</x:v>
-      </x:c>
-      <x:c r="B98" t="str">
-        <x:v>test_far_error_rate_abs_ge_20</x:v>
-      </x:c>
-      <x:c r="C98" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D98" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E98" t="n">
-        <x:v>0.09090909090909091</x:v>
-      </x:c>
-      <x:c r="F98" t="str">
-        <x:v>needs_review</x:v>
-      </x:c>
-      <x:c r="G98" t="str">
-        <x:v>B1-best</x:v>
-      </x:c>
-      <x:c r="H98" t="str">
-        <x:v>未被规则自动归类。</x:v>
-      </x:c>
-      <x:c r="I98" t="str">
-        <x:v>人工抽查源文件。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -44666,76 +44203,76 @@
         <x:v>test_selection_rate_std</x:v>
       </x:c>
       <x:c r="AI1" t="str">
+        <x:v>val_high_angle_macro_f1_mean</x:v>
+      </x:c>
+      <x:c r="AJ1" t="str">
+        <x:v>val_high_angle_macro_f1_std</x:v>
+      </x:c>
+      <x:c r="AK1" t="str">
+        <x:v>test_high_angle_macro_f1_mean</x:v>
+      </x:c>
+      <x:c r="AL1" t="str">
+        <x:v>test_high_angle_macro_f1_std</x:v>
+      </x:c>
+      <x:c r="AM1" t="str">
         <x:v>val_gate_tot_mean_mean</x:v>
       </x:c>
-      <x:c r="AJ1" t="str">
+      <x:c r="AN1" t="str">
         <x:v>val_gate_tot_mean_std</x:v>
       </x:c>
-      <x:c r="AK1" t="str">
+      <x:c r="AO1" t="str">
         <x:v>test_gate_tot_mean_mean</x:v>
       </x:c>
-      <x:c r="AL1" t="str">
+      <x:c r="AP1" t="str">
         <x:v>test_gate_tot_mean_std</x:v>
       </x:c>
-      <x:c r="AM1" t="str">
+      <x:c r="AQ1" t="str">
         <x:v>val_gate_toa_mean_mean</x:v>
       </x:c>
-      <x:c r="AN1" t="str">
+      <x:c r="AR1" t="str">
         <x:v>val_gate_toa_mean_std</x:v>
       </x:c>
-      <x:c r="AO1" t="str">
+      <x:c r="AS1" t="str">
         <x:v>test_gate_toa_mean_mean</x:v>
       </x:c>
-      <x:c r="AP1" t="str">
+      <x:c r="AT1" t="str">
         <x:v>test_gate_toa_mean_std</x:v>
       </x:c>
-      <x:c r="AQ1" t="str">
+      <x:c r="AU1" t="str">
         <x:v>val_film_gamma_abs_mean_mean</x:v>
       </x:c>
-      <x:c r="AR1" t="str">
+      <x:c r="AV1" t="str">
         <x:v>val_film_gamma_abs_mean_std</x:v>
       </x:c>
-      <x:c r="AS1" t="str">
+      <x:c r="AW1" t="str">
         <x:v>test_film_gamma_abs_mean_mean</x:v>
       </x:c>
-      <x:c r="AT1" t="str">
+      <x:c r="AX1" t="str">
         <x:v>test_film_gamma_abs_mean_std</x:v>
       </x:c>
-      <x:c r="AU1" t="str">
+      <x:c r="AY1" t="str">
         <x:v>val_film_beta_abs_mean_mean</x:v>
       </x:c>
-      <x:c r="AV1" t="str">
+      <x:c r="AZ1" t="str">
         <x:v>val_film_beta_abs_mean_std</x:v>
       </x:c>
-      <x:c r="AW1" t="str">
+      <x:c r="BA1" t="str">
         <x:v>test_film_beta_abs_mean_mean</x:v>
       </x:c>
-      <x:c r="AX1" t="str">
+      <x:c r="BB1" t="str">
         <x:v>test_film_beta_abs_mean_std</x:v>
       </x:c>
-      <x:c r="AY1" t="str">
+      <x:c r="BC1" t="str">
         <x:v>test_seconds_mean</x:v>
       </x:c>
-      <x:c r="AZ1" t="str">
+      <x:c r="BD1" t="str">
         <x:v>test_seconds_std</x:v>
       </x:c>
-      <x:c r="BA1" t="str">
-        <x:v>val_high_angle_macro_f1_mean</x:v>
-      </x:c>
-      <x:c r="BB1" t="str">
-        <x:v>val_high_angle_macro_f1_std</x:v>
-      </x:c>
-      <x:c r="BC1" t="str">
+      <x:c r="BE1" t="str">
         <x:v>val_far_error_rate_abs_ge_20_mean</x:v>
       </x:c>
-      <x:c r="BD1" t="str">
+      <x:c r="BF1" t="str">
         <x:v>val_far_error_rate_abs_ge_20_std</x:v>
-      </x:c>
-      <x:c r="BE1" t="str">
-        <x:v>test_high_angle_macro_f1_mean</x:v>
-      </x:c>
-      <x:c r="BF1" t="str">
-        <x:v>test_high_angle_macro_f1_std</x:v>
       </x:c>
       <x:c r="BG1" t="str">
         <x:v>test_far_error_rate_abs_ge_20_mean</x:v>
@@ -44772,30 +44309,6 @@
       </x:c>
       <x:c r="BR1" t="str">
         <x:v>handcrafted_features</x:v>
-      </x:c>
-      <x:c r="BS1" t="str">
-        <x:v>val_confusion_45_50_mean</x:v>
-      </x:c>
-      <x:c r="BT1" t="str">
-        <x:v>val_confusion_45_50_std</x:v>
-      </x:c>
-      <x:c r="BU1" t="str">
-        <x:v>test_confusion_45_50_mean</x:v>
-      </x:c>
-      <x:c r="BV1" t="str">
-        <x:v>test_confusion_45_50_std</x:v>
-      </x:c>
-      <x:c r="BW1" t="str">
-        <x:v>val_confusion_60_70_mean</x:v>
-      </x:c>
-      <x:c r="BX1" t="str">
-        <x:v>val_confusion_60_70_std</x:v>
-      </x:c>
-      <x:c r="BY1" t="str">
-        <x:v>test_confusion_60_70_mean</x:v>
-      </x:c>
-      <x:c r="BZ1" t="str">
-        <x:v>test_confusion_60_70_std</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -44901,10 +44414,18 @@
       <x:c r="AH2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI2"/>
-      <x:c r="AJ2"/>
-      <x:c r="AK2"/>
-      <x:c r="AL2"/>
+      <x:c r="AI2" t="n">
+        <x:v>0.6723693152</x:v>
+      </x:c>
+      <x:c r="AJ2" t="n">
+        <x:v>0.01104396161</x:v>
+      </x:c>
+      <x:c r="AK2" t="n">
+        <x:v>0.6963085162</x:v>
+      </x:c>
+      <x:c r="AL2" t="n">
+        <x:v>0.0101231561</x:v>
+      </x:c>
       <x:c r="AM2"/>
       <x:c r="AN2"/>
       <x:c r="AO2"/>
@@ -44937,14 +44458,6 @@
       <x:c r="BP2"/>
       <x:c r="BQ2"/>
       <x:c r="BR2"/>
-      <x:c r="BS2"/>
-      <x:c r="BT2"/>
-      <x:c r="BU2"/>
-      <x:c r="BV2"/>
-      <x:c r="BW2"/>
-      <x:c r="BX2"/>
-      <x:c r="BY2"/>
-      <x:c r="BZ2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -45049,10 +44562,18 @@
       <x:c r="AH3" t="n">
         <x:v>0.02436908682</x:v>
       </x:c>
-      <x:c r="AI3"/>
-      <x:c r="AJ3"/>
-      <x:c r="AK3"/>
-      <x:c r="AL3"/>
+      <x:c r="AI3" t="n">
+        <x:v>0.7894858673</x:v>
+      </x:c>
+      <x:c r="AJ3" t="n">
+        <x:v>0.02094811862</x:v>
+      </x:c>
+      <x:c r="AK3" t="n">
+        <x:v>0.8127623542</x:v>
+      </x:c>
+      <x:c r="AL3" t="n">
+        <x:v>0.01514092265</x:v>
+      </x:c>
       <x:c r="AM3"/>
       <x:c r="AN3"/>
       <x:c r="AO3"/>
@@ -45085,14 +44606,6 @@
       <x:c r="BP3"/>
       <x:c r="BQ3"/>
       <x:c r="BR3"/>
-      <x:c r="BS3"/>
-      <x:c r="BT3"/>
-      <x:c r="BU3"/>
-      <x:c r="BV3"/>
-      <x:c r="BW3"/>
-      <x:c r="BX3"/>
-      <x:c r="BY3"/>
-      <x:c r="BZ3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -45197,10 +44710,18 @@
       <x:c r="AH4" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI4"/>
-      <x:c r="AJ4"/>
-      <x:c r="AK4"/>
-      <x:c r="AL4"/>
+      <x:c r="AI4" t="n">
+        <x:v>0.7184152741</x:v>
+      </x:c>
+      <x:c r="AJ4" t="n">
+        <x:v>0.008053869367</x:v>
+      </x:c>
+      <x:c r="AK4" t="n">
+        <x:v>0.7130526697</x:v>
+      </x:c>
+      <x:c r="AL4" t="n">
+        <x:v>0.003839576654</x:v>
+      </x:c>
       <x:c r="AM4"/>
       <x:c r="AN4"/>
       <x:c r="AO4"/>
@@ -45233,14 +44754,6 @@
       <x:c r="BP4"/>
       <x:c r="BQ4"/>
       <x:c r="BR4"/>
-      <x:c r="BS4"/>
-      <x:c r="BT4"/>
-      <x:c r="BU4"/>
-      <x:c r="BV4"/>
-      <x:c r="BW4"/>
-      <x:c r="BX4"/>
-      <x:c r="BY4"/>
-      <x:c r="BZ4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
@@ -45345,10 +44858,18 @@
       <x:c r="AH5" t="n">
         <x:v>0.05404788693</x:v>
       </x:c>
-      <x:c r="AI5"/>
-      <x:c r="AJ5"/>
-      <x:c r="AK5"/>
-      <x:c r="AL5"/>
+      <x:c r="AI5" t="n">
+        <x:v>0.719471647</x:v>
+      </x:c>
+      <x:c r="AJ5" t="n">
+        <x:v>0.0123091747</x:v>
+      </x:c>
+      <x:c r="AK5" t="n">
+        <x:v>0.7217994263</x:v>
+      </x:c>
+      <x:c r="AL5" t="n">
+        <x:v>0.004125695961</x:v>
+      </x:c>
       <x:c r="AM5"/>
       <x:c r="AN5"/>
       <x:c r="AO5"/>
@@ -45381,14 +44902,6 @@
       <x:c r="BP5"/>
       <x:c r="BQ5"/>
       <x:c r="BR5"/>
-      <x:c r="BS5"/>
-      <x:c r="BT5"/>
-      <x:c r="BU5"/>
-      <x:c r="BV5"/>
-      <x:c r="BW5"/>
-      <x:c r="BX5"/>
-      <x:c r="BY5"/>
-      <x:c r="BZ5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
@@ -45485,10 +44998,18 @@
       <x:c r="AF6"/>
       <x:c r="AG6"/>
       <x:c r="AH6"/>
-      <x:c r="AI6"/>
-      <x:c r="AJ6"/>
-      <x:c r="AK6"/>
-      <x:c r="AL6"/>
+      <x:c r="AI6" t="n">
+        <x:v>0.6723693152</x:v>
+      </x:c>
+      <x:c r="AJ6" t="n">
+        <x:v>0.01104396161</x:v>
+      </x:c>
+      <x:c r="AK6" t="n">
+        <x:v>0.6963085162</x:v>
+      </x:c>
+      <x:c r="AL6" t="n">
+        <x:v>0.0101231561</x:v>
+      </x:c>
       <x:c r="AM6"/>
       <x:c r="AN6"/>
       <x:c r="AO6"/>
@@ -45521,14 +45042,6 @@
       <x:c r="BP6"/>
       <x:c r="BQ6"/>
       <x:c r="BR6"/>
-      <x:c r="BS6"/>
-      <x:c r="BT6"/>
-      <x:c r="BU6"/>
-      <x:c r="BV6"/>
-      <x:c r="BW6"/>
-      <x:c r="BX6"/>
-      <x:c r="BY6"/>
-      <x:c r="BZ6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
@@ -45625,10 +45138,18 @@
       <x:c r="AF7"/>
       <x:c r="AG7"/>
       <x:c r="AH7"/>
-      <x:c r="AI7"/>
-      <x:c r="AJ7"/>
-      <x:c r="AK7"/>
-      <x:c r="AL7"/>
+      <x:c r="AI7" t="n">
+        <x:v>0.7894858673</x:v>
+      </x:c>
+      <x:c r="AJ7" t="n">
+        <x:v>0.02094811862</x:v>
+      </x:c>
+      <x:c r="AK7" t="n">
+        <x:v>0.8127623542</x:v>
+      </x:c>
+      <x:c r="AL7" t="n">
+        <x:v>0.01514092265</x:v>
+      </x:c>
       <x:c r="AM7"/>
       <x:c r="AN7"/>
       <x:c r="AO7"/>
@@ -45661,14 +45182,6 @@
       <x:c r="BP7"/>
       <x:c r="BQ7"/>
       <x:c r="BR7"/>
-      <x:c r="BS7"/>
-      <x:c r="BT7"/>
-      <x:c r="BU7"/>
-      <x:c r="BV7"/>
-      <x:c r="BW7"/>
-      <x:c r="BX7"/>
-      <x:c r="BY7"/>
-      <x:c r="BZ7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
@@ -45765,10 +45278,18 @@
       <x:c r="AF8"/>
       <x:c r="AG8"/>
       <x:c r="AH8"/>
-      <x:c r="AI8"/>
-      <x:c r="AJ8"/>
-      <x:c r="AK8"/>
-      <x:c r="AL8"/>
+      <x:c r="AI8" t="n">
+        <x:v>0.7184152741</x:v>
+      </x:c>
+      <x:c r="AJ8" t="n">
+        <x:v>0.008053869367</x:v>
+      </x:c>
+      <x:c r="AK8" t="n">
+        <x:v>0.7130526697</x:v>
+      </x:c>
+      <x:c r="AL8" t="n">
+        <x:v>0.003839576654</x:v>
+      </x:c>
       <x:c r="AM8"/>
       <x:c r="AN8"/>
       <x:c r="AO8"/>
@@ -45801,14 +45322,6 @@
       <x:c r="BP8"/>
       <x:c r="BQ8"/>
       <x:c r="BR8"/>
-      <x:c r="BS8"/>
-      <x:c r="BT8"/>
-      <x:c r="BU8"/>
-      <x:c r="BV8"/>
-      <x:c r="BW8"/>
-      <x:c r="BX8"/>
-      <x:c r="BY8"/>
-      <x:c r="BZ8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="str">
@@ -45905,10 +45418,18 @@
       <x:c r="AF9"/>
       <x:c r="AG9"/>
       <x:c r="AH9"/>
-      <x:c r="AI9"/>
-      <x:c r="AJ9"/>
-      <x:c r="AK9"/>
-      <x:c r="AL9"/>
+      <x:c r="AI9" t="n">
+        <x:v>0.7272936395</x:v>
+      </x:c>
+      <x:c r="AJ9" t="n">
+        <x:v>0.004825065936</x:v>
+      </x:c>
+      <x:c r="AK9" t="n">
+        <x:v>0.7470134734</x:v>
+      </x:c>
+      <x:c r="AL9" t="n">
+        <x:v>0.009289209185</x:v>
+      </x:c>
       <x:c r="AM9"/>
       <x:c r="AN9"/>
       <x:c r="AO9"/>
@@ -45941,14 +45462,6 @@
       <x:c r="BP9"/>
       <x:c r="BQ9"/>
       <x:c r="BR9"/>
-      <x:c r="BS9"/>
-      <x:c r="BT9"/>
-      <x:c r="BU9"/>
-      <x:c r="BV9"/>
-      <x:c r="BW9"/>
-      <x:c r="BX9"/>
-      <x:c r="BY9"/>
-      <x:c r="BZ9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="str">
@@ -46053,10 +45566,18 @@
       <x:c r="AH10" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI10"/>
-      <x:c r="AJ10"/>
-      <x:c r="AK10"/>
-      <x:c r="AL10"/>
+      <x:c r="AI10" t="n">
+        <x:v>0.6723693152</x:v>
+      </x:c>
+      <x:c r="AJ10" t="n">
+        <x:v>0.01104396161</x:v>
+      </x:c>
+      <x:c r="AK10" t="n">
+        <x:v>0.6963085162</x:v>
+      </x:c>
+      <x:c r="AL10" t="n">
+        <x:v>0.0101231561</x:v>
+      </x:c>
       <x:c r="AM10"/>
       <x:c r="AN10"/>
       <x:c r="AO10"/>
@@ -46089,14 +45610,6 @@
       <x:c r="BP10"/>
       <x:c r="BQ10"/>
       <x:c r="BR10"/>
-      <x:c r="BS10"/>
-      <x:c r="BT10"/>
-      <x:c r="BU10"/>
-      <x:c r="BV10"/>
-      <x:c r="BW10"/>
-      <x:c r="BX10"/>
-      <x:c r="BY10"/>
-      <x:c r="BZ10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="str">
@@ -46201,10 +45714,18 @@
       <x:c r="AH11" t="n">
         <x:v>0.02436908682</x:v>
       </x:c>
-      <x:c r="AI11"/>
-      <x:c r="AJ11"/>
-      <x:c r="AK11"/>
-      <x:c r="AL11"/>
+      <x:c r="AI11" t="n">
+        <x:v>0.7894858673</x:v>
+      </x:c>
+      <x:c r="AJ11" t="n">
+        <x:v>0.02094811862</x:v>
+      </x:c>
+      <x:c r="AK11" t="n">
+        <x:v>0.8127623542</x:v>
+      </x:c>
+      <x:c r="AL11" t="n">
+        <x:v>0.01514092265</x:v>
+      </x:c>
       <x:c r="AM11"/>
       <x:c r="AN11"/>
       <x:c r="AO11"/>
@@ -46237,14 +45758,6 @@
       <x:c r="BP11"/>
       <x:c r="BQ11"/>
       <x:c r="BR11"/>
-      <x:c r="BS11"/>
-      <x:c r="BT11"/>
-      <x:c r="BU11"/>
-      <x:c r="BV11"/>
-      <x:c r="BW11"/>
-      <x:c r="BX11"/>
-      <x:c r="BY11"/>
-      <x:c r="BZ11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
@@ -46349,10 +45862,18 @@
       <x:c r="AH12" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AI12"/>
-      <x:c r="AJ12"/>
-      <x:c r="AK12"/>
-      <x:c r="AL12"/>
+      <x:c r="AI12" t="n">
+        <x:v>0.7184152741</x:v>
+      </x:c>
+      <x:c r="AJ12" t="n">
+        <x:v>0.008053869367</x:v>
+      </x:c>
+      <x:c r="AK12" t="n">
+        <x:v>0.7130526697</x:v>
+      </x:c>
+      <x:c r="AL12" t="n">
+        <x:v>0.003839576654</x:v>
+      </x:c>
       <x:c r="AM12"/>
       <x:c r="AN12"/>
       <x:c r="AO12"/>
@@ -46385,14 +45906,6 @@
       <x:c r="BP12"/>
       <x:c r="BQ12"/>
       <x:c r="BR12"/>
-      <x:c r="BS12"/>
-      <x:c r="BT12"/>
-      <x:c r="BU12"/>
-      <x:c r="BV12"/>
-      <x:c r="BW12"/>
-      <x:c r="BX12"/>
-      <x:c r="BY12"/>
-      <x:c r="BZ12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="str">
@@ -46497,10 +46010,18 @@
       <x:c r="AH13" t="n">
         <x:v>0.3332620173</x:v>
       </x:c>
-      <x:c r="AI13"/>
-      <x:c r="AJ13"/>
-      <x:c r="AK13"/>
-      <x:c r="AL13"/>
+      <x:c r="AI13" t="n">
+        <x:v>0.7284732828</x:v>
+      </x:c>
+      <x:c r="AJ13" t="n">
+        <x:v>0.00791450348</x:v>
+      </x:c>
+      <x:c r="AK13" t="n">
+        <x:v>0.7322993306</x:v>
+      </x:c>
+      <x:c r="AL13" t="n">
+        <x:v>0.003714472761</x:v>
+      </x:c>
       <x:c r="AM13"/>
       <x:c r="AN13"/>
       <x:c r="AO13"/>
@@ -46533,14 +46054,6 @@
       <x:c r="BP13"/>
       <x:c r="BQ13"/>
       <x:c r="BR13"/>
-      <x:c r="BS13"/>
-      <x:c r="BT13"/>
-      <x:c r="BU13"/>
-      <x:c r="BV13"/>
-      <x:c r="BW13"/>
-      <x:c r="BX13"/>
-      <x:c r="BY13"/>
-      <x:c r="BZ13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="str">
@@ -46635,10 +46148,18 @@
       <x:c r="AF14"/>
       <x:c r="AG14"/>
       <x:c r="AH14"/>
-      <x:c r="AI14"/>
-      <x:c r="AJ14"/>
-      <x:c r="AK14"/>
-      <x:c r="AL14"/>
+      <x:c r="AI14" t="n">
+        <x:v>0.7070502787</x:v>
+      </x:c>
+      <x:c r="AJ14" t="n">
+        <x:v>0.01083278279</x:v>
+      </x:c>
+      <x:c r="AK14" t="n">
+        <x:v>0.7494376188</x:v>
+      </x:c>
+      <x:c r="AL14" t="n">
+        <x:v>0.01113824166</x:v>
+      </x:c>
       <x:c r="AM14"/>
       <x:c r="AN14"/>
       <x:c r="AO14"/>
@@ -46651,29 +46172,21 @@
       <x:c r="AV14"/>
       <x:c r="AW14"/>
       <x:c r="AX14"/>
-      <x:c r="AY14" t="n">
+      <x:c r="AY14"/>
+      <x:c r="AZ14"/>
+      <x:c r="BA14"/>
+      <x:c r="BB14"/>
+      <x:c r="BC14" t="n">
         <x:v>0.5190684656</x:v>
       </x:c>
-      <x:c r="AZ14" t="n">
+      <x:c r="BD14" t="n">
         <x:v>0.02695580304</x:v>
       </x:c>
-      <x:c r="BA14" t="n">
-        <x:v>0.7070502787</x:v>
-      </x:c>
-      <x:c r="BB14" t="n">
-        <x:v>0.01083278279</x:v>
-      </x:c>
-      <x:c r="BC14" t="n">
+      <x:c r="BE14" t="n">
         <x:v>0.1068931069</x:v>
       </x:c>
-      <x:c r="BD14" t="n">
+      <x:c r="BF14" t="n">
         <x:v>0.006238759239</x:v>
-      </x:c>
-      <x:c r="BE14" t="n">
-        <x:v>0.7494376188</x:v>
-      </x:c>
-      <x:c r="BF14" t="n">
-        <x:v>0.01113824166</x:v>
       </x:c>
       <x:c r="BG14" t="n">
         <x:v>0.08217362492</x:v>
@@ -46691,14 +46204,6 @@
       <x:c r="BP14"/>
       <x:c r="BQ14"/>
       <x:c r="BR14"/>
-      <x:c r="BS14"/>
-      <x:c r="BT14"/>
-      <x:c r="BU14"/>
-      <x:c r="BV14"/>
-      <x:c r="BW14"/>
-      <x:c r="BX14"/>
-      <x:c r="BY14"/>
-      <x:c r="BZ14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="str">
@@ -46794,60 +46299,60 @@
       <x:c r="AG15"/>
       <x:c r="AH15"/>
       <x:c r="AI15" t="n">
+        <x:v>0.7012315546</x:v>
+      </x:c>
+      <x:c r="AJ15" t="n">
+        <x:v>0.01221282842</x:v>
+      </x:c>
+      <x:c r="AK15" t="n">
+        <x:v>0.7403053461</x:v>
+      </x:c>
+      <x:c r="AL15" t="n">
+        <x:v>0.00660475241</x:v>
+      </x:c>
+      <x:c r="AM15" t="n">
         <x:v>0.7763057152</x:v>
       </x:c>
-      <x:c r="AJ15" t="n">
+      <x:c r="AN15" t="n">
         <x:v>0.01544480083</x:v>
       </x:c>
-      <x:c r="AK15" t="n">
+      <x:c r="AO15" t="n">
         <x:v>0.7762409846</x:v>
       </x:c>
-      <x:c r="AL15" t="n">
+      <x:c r="AP15" t="n">
         <x:v>0.01462524134</x:v>
       </x:c>
-      <x:c r="AM15" t="n">
+      <x:c r="AQ15" t="n">
         <x:v>0.2236941109</x:v>
       </x:c>
-      <x:c r="AN15" t="n">
+      <x:c r="AR15" t="n">
         <x:v>0.01543888026</x:v>
       </x:c>
-      <x:c r="AO15" t="n">
+      <x:c r="AS15" t="n">
         <x:v>0.2237617572</x:v>
       </x:c>
-      <x:c r="AP15" t="n">
+      <x:c r="AT15" t="n">
         <x:v>0.01462150929</x:v>
       </x:c>
-      <x:c r="AQ15"/>
-      <x:c r="AR15"/>
-      <x:c r="AS15"/>
-      <x:c r="AT15"/>
       <x:c r="AU15"/>
       <x:c r="AV15"/>
       <x:c r="AW15"/>
       <x:c r="AX15"/>
-      <x:c r="AY15" t="n">
+      <x:c r="AY15"/>
+      <x:c r="AZ15"/>
+      <x:c r="BA15"/>
+      <x:c r="BB15"/>
+      <x:c r="BC15" t="n">
         <x:v>0.5579922988</x:v>
       </x:c>
-      <x:c r="AZ15" t="n">
+      <x:c r="BD15" t="n">
         <x:v>0.01893490799</x:v>
       </x:c>
-      <x:c r="BA15" t="n">
-        <x:v>0.7012315546</x:v>
-      </x:c>
-      <x:c r="BB15" t="n">
-        <x:v>0.01221282842</x:v>
-      </x:c>
-      <x:c r="BC15" t="n">
+      <x:c r="BE15" t="n">
         <x:v>0.0969030969</x:v>
       </x:c>
-      <x:c r="BD15" t="n">
+      <x:c r="BF15" t="n">
         <x:v>0.006993006993</x:v>
-      </x:c>
-      <x:c r="BE15" t="n">
-        <x:v>0.7403053461</x:v>
-      </x:c>
-      <x:c r="BF15" t="n">
-        <x:v>0.00660475241</x:v>
       </x:c>
       <x:c r="BG15" t="n">
         <x:v>0.08681245858</x:v>
@@ -46865,14 +46370,6 @@
       <x:c r="BP15"/>
       <x:c r="BQ15"/>
       <x:c r="BR15"/>
-      <x:c r="BS15"/>
-      <x:c r="BT15"/>
-      <x:c r="BU15"/>
-      <x:c r="BV15"/>
-      <x:c r="BW15"/>
-      <x:c r="BX15"/>
-      <x:c r="BY15"/>
-      <x:c r="BZ15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
@@ -46967,61 +46464,61 @@
       <x:c r="AF16"/>
       <x:c r="AG16"/>
       <x:c r="AH16"/>
-      <x:c r="AI16"/>
-      <x:c r="AJ16"/>
-      <x:c r="AK16"/>
-      <x:c r="AL16"/>
+      <x:c r="AI16" t="n">
+        <x:v>0.7090519367</x:v>
+      </x:c>
+      <x:c r="AJ16" t="n">
+        <x:v>0.006245185169</x:v>
+      </x:c>
+      <x:c r="AK16" t="n">
+        <x:v>0.7432719746</x:v>
+      </x:c>
+      <x:c r="AL16" t="n">
+        <x:v>0.01197911134</x:v>
+      </x:c>
       <x:c r="AM16"/>
       <x:c r="AN16"/>
       <x:c r="AO16"/>
       <x:c r="AP16"/>
-      <x:c r="AQ16" t="n">
+      <x:c r="AQ16"/>
+      <x:c r="AR16"/>
+      <x:c r="AS16"/>
+      <x:c r="AT16"/>
+      <x:c r="AU16" t="n">
         <x:v>0.04112120718</x:v>
       </x:c>
-      <x:c r="AR16" t="n">
+      <x:c r="AV16" t="n">
         <x:v>0.01412688071</x:v>
       </x:c>
-      <x:c r="AS16" t="n">
+      <x:c r="AW16" t="n">
         <x:v>0.04053514016</x:v>
       </x:c>
-      <x:c r="AT16" t="n">
+      <x:c r="AX16" t="n">
         <x:v>0.01408795593</x:v>
       </x:c>
-      <x:c r="AU16" t="n">
+      <x:c r="AY16" t="n">
         <x:v>0.05128242448</x:v>
       </x:c>
-      <x:c r="AV16" t="n">
+      <x:c r="AZ16" t="n">
         <x:v>0.01742893204</x:v>
       </x:c>
-      <x:c r="AW16" t="n">
+      <x:c r="BA16" t="n">
         <x:v>0.05054960524</x:v>
       </x:c>
-      <x:c r="AX16" t="n">
+      <x:c r="BB16" t="n">
         <x:v>0.01742976926</x:v>
       </x:c>
-      <x:c r="AY16" t="n">
+      <x:c r="BC16" t="n">
         <x:v>0.5610241201</x:v>
       </x:c>
-      <x:c r="AZ16" t="n">
+      <x:c r="BD16" t="n">
         <x:v>0.04830271038</x:v>
       </x:c>
-      <x:c r="BA16" t="n">
-        <x:v>0.7090519367</x:v>
-      </x:c>
-      <x:c r="BB16" t="n">
-        <x:v>0.006245185169</x:v>
-      </x:c>
-      <x:c r="BC16" t="n">
+      <x:c r="BE16" t="n">
         <x:v>0.1025641026</x:v>
       </x:c>
-      <x:c r="BD16" t="n">
+      <x:c r="BF16" t="n">
         <x:v>0.003211338915</x:v>
-      </x:c>
-      <x:c r="BE16" t="n">
-        <x:v>0.7432719746</x:v>
-      </x:c>
-      <x:c r="BF16" t="n">
-        <x:v>0.01197911134</x:v>
       </x:c>
       <x:c r="BG16" t="n">
         <x:v>0.08648111332</x:v>
@@ -47039,14 +46536,6 @@
       <x:c r="BP16"/>
       <x:c r="BQ16"/>
       <x:c r="BR16"/>
-      <x:c r="BS16"/>
-      <x:c r="BT16"/>
-      <x:c r="BU16"/>
-      <x:c r="BV16"/>
-      <x:c r="BW16"/>
-      <x:c r="BX16"/>
-      <x:c r="BY16"/>
-      <x:c r="BZ16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
@@ -47142,60 +46631,60 @@
       <x:c r="AG17"/>
       <x:c r="AH17"/>
       <x:c r="AI17" t="n">
+        <x:v>0.6966768107</x:v>
+      </x:c>
+      <x:c r="AJ17" t="n">
+        <x:v>0.01889003586</x:v>
+      </x:c>
+      <x:c r="AK17" t="n">
+        <x:v>0.714572462</x:v>
+      </x:c>
+      <x:c r="AL17" t="n">
+        <x:v>0.03165844592</x:v>
+      </x:c>
+      <x:c r="AM17" t="n">
         <x:v>0.4337807397</x:v>
       </x:c>
-      <x:c r="AJ17" t="n">
+      <x:c r="AN17" t="n">
         <x:v>0.1216589044</x:v>
       </x:c>
-      <x:c r="AK17" t="n">
+      <x:c r="AO17" t="n">
         <x:v>0.4346568584</x:v>
       </x:c>
-      <x:c r="AL17" t="n">
+      <x:c r="AP17" t="n">
         <x:v>0.1218870765</x:v>
       </x:c>
-      <x:c r="AM17" t="n">
+      <x:c r="AQ17" t="n">
         <x:v>0.5662208498</x:v>
       </x:c>
-      <x:c r="AN17" t="n">
+      <x:c r="AR17" t="n">
         <x:v>0.1216565487</x:v>
       </x:c>
-      <x:c r="AO17" t="n">
+      <x:c r="AS17" t="n">
         <x:v>0.5653431714</x:v>
       </x:c>
-      <x:c r="AP17" t="n">
+      <x:c r="AT17" t="n">
         <x:v>0.1218858996</x:v>
       </x:c>
-      <x:c r="AQ17"/>
-      <x:c r="AR17"/>
-      <x:c r="AS17"/>
-      <x:c r="AT17"/>
       <x:c r="AU17"/>
       <x:c r="AV17"/>
       <x:c r="AW17"/>
       <x:c r="AX17"/>
-      <x:c r="AY17" t="n">
+      <x:c r="AY17"/>
+      <x:c r="AZ17"/>
+      <x:c r="BA17"/>
+      <x:c r="BB17"/>
+      <x:c r="BC17" t="n">
         <x:v>0.5707638372</x:v>
       </x:c>
-      <x:c r="AZ17" t="n">
+      <x:c r="BD17" t="n">
         <x:v>0.02946644103</x:v>
       </x:c>
-      <x:c r="BA17" t="n">
-        <x:v>0.6966768107</x:v>
-      </x:c>
-      <x:c r="BB17" t="n">
-        <x:v>0.01889003586</x:v>
-      </x:c>
-      <x:c r="BC17" t="n">
+      <x:c r="BE17" t="n">
         <x:v>0.1122211122</x:v>
       </x:c>
-      <x:c r="BD17" t="n">
+      <x:c r="BF17" t="n">
         <x:v>0.005028194762</x:v>
-      </x:c>
-      <x:c r="BE17" t="n">
-        <x:v>0.714572462</x:v>
-      </x:c>
-      <x:c r="BF17" t="n">
-        <x:v>0.03165844592</x:v>
       </x:c>
       <x:c r="BG17" t="n">
         <x:v>0.09178263751</x:v>
@@ -47231,14 +46720,6 @@
         <x:v>0.1218858996</x:v>
       </x:c>
       <x:c r="BR17"/>
-      <x:c r="BS17"/>
-      <x:c r="BT17"/>
-      <x:c r="BU17"/>
-      <x:c r="BV17"/>
-      <x:c r="BW17"/>
-      <x:c r="BX17"/>
-      <x:c r="BY17"/>
-      <x:c r="BZ17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
@@ -47334,60 +46815,60 @@
       <x:c r="AG18"/>
       <x:c r="AH18"/>
       <x:c r="AI18" t="n">
+        <x:v>0.7192912517</x:v>
+      </x:c>
+      <x:c r="AJ18" t="n">
+        <x:v>0.01042063073</x:v>
+      </x:c>
+      <x:c r="AK18" t="n">
+        <x:v>0.742124124</x:v>
+      </x:c>
+      <x:c r="AL18" t="n">
+        <x:v>0.01927520485</x:v>
+      </x:c>
+      <x:c r="AM18" t="n">
         <x:v>0.3479498972</x:v>
       </x:c>
-      <x:c r="AJ18" t="n">
+      <x:c r="AN18" t="n">
         <x:v>0.2430851121</x:v>
       </x:c>
-      <x:c r="AK18" t="n">
+      <x:c r="AO18" t="n">
         <x:v>0.3489330957</x:v>
       </x:c>
-      <x:c r="AL18" t="n">
+      <x:c r="AP18" t="n">
         <x:v>0.2462871208</x:v>
       </x:c>
-      <x:c r="AM18" t="n">
+      <x:c r="AQ18" t="n">
         <x:v>0.6520502865</x:v>
       </x:c>
-      <x:c r="AN18" t="n">
+      <x:c r="AR18" t="n">
         <x:v>0.2430832584</x:v>
       </x:c>
-      <x:c r="AO18" t="n">
+      <x:c r="AS18" t="n">
         <x:v>0.6510670781</x:v>
       </x:c>
-      <x:c r="AP18" t="n">
+      <x:c r="AT18" t="n">
         <x:v>0.2462897834</x:v>
       </x:c>
-      <x:c r="AQ18"/>
-      <x:c r="AR18"/>
-      <x:c r="AS18"/>
-      <x:c r="AT18"/>
       <x:c r="AU18"/>
       <x:c r="AV18"/>
       <x:c r="AW18"/>
       <x:c r="AX18"/>
-      <x:c r="AY18" t="n">
+      <x:c r="AY18"/>
+      <x:c r="AZ18"/>
+      <x:c r="BA18"/>
+      <x:c r="BB18"/>
+      <x:c r="BC18" t="n">
         <x:v>0.5639540913</x:v>
       </x:c>
-      <x:c r="AZ18" t="n">
+      <x:c r="BD18" t="n">
         <x:v>0.02459332968</x:v>
       </x:c>
-      <x:c r="BA18" t="n">
-        <x:v>0.7192912517</x:v>
-      </x:c>
-      <x:c r="BB18" t="n">
-        <x:v>0.01042063073</x:v>
-      </x:c>
-      <x:c r="BC18" t="n">
+      <x:c r="BE18" t="n">
         <x:v>0.1025641026</x:v>
       </x:c>
-      <x:c r="BD18" t="n">
+      <x:c r="BF18" t="n">
         <x:v>0.006499907191</x:v>
-      </x:c>
-      <x:c r="BE18" t="n">
-        <x:v>0.742124124</x:v>
-      </x:c>
-      <x:c r="BF18" t="n">
-        <x:v>0.01927520485</x:v>
       </x:c>
       <x:c r="BG18" t="n">
         <x:v>0.09310801856</x:v>
@@ -47423,14 +46904,6 @@
         <x:v>0.2462897834</x:v>
       </x:c>
       <x:c r="BR18"/>
-      <x:c r="BS18"/>
-      <x:c r="BT18"/>
-      <x:c r="BU18"/>
-      <x:c r="BV18"/>
-      <x:c r="BW18"/>
-      <x:c r="BX18"/>
-      <x:c r="BY18"/>
-      <x:c r="BZ18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
@@ -47526,60 +46999,60 @@
       <x:c r="AG19"/>
       <x:c r="AH19"/>
       <x:c r="AI19" t="n">
+        <x:v>0.7125380877</x:v>
+      </x:c>
+      <x:c r="AJ19" t="n">
+        <x:v>0.01178997492</x:v>
+      </x:c>
+      <x:c r="AK19" t="n">
+        <x:v>0.7429121934</x:v>
+      </x:c>
+      <x:c r="AL19" t="n">
+        <x:v>0.00356150143</x:v>
+      </x:c>
+      <x:c r="AM19" t="n">
         <x:v>0.7933802803</x:v>
       </x:c>
-      <x:c r="AJ19" t="n">
+      <x:c r="AN19" t="n">
         <x:v>0.01442460089</x:v>
       </x:c>
-      <x:c r="AK19" t="n">
+      <x:c r="AO19" t="n">
         <x:v>0.793725272</x:v>
       </x:c>
-      <x:c r="AL19" t="n">
+      <x:c r="AP19" t="n">
         <x:v>0.01492912894</x:v>
       </x:c>
-      <x:c r="AM19" t="n">
+      <x:c r="AQ19" t="n">
         <x:v>0.2066214184</x:v>
       </x:c>
-      <x:c r="AN19" t="n">
+      <x:c r="AR19" t="n">
         <x:v>0.01442720208</x:v>
       </x:c>
-      <x:c r="AO19" t="n">
+      <x:c r="AS19" t="n">
         <x:v>0.2062789698</x:v>
       </x:c>
-      <x:c r="AP19" t="n">
+      <x:c r="AT19" t="n">
         <x:v>0.0149346702</x:v>
       </x:c>
-      <x:c r="AQ19"/>
-      <x:c r="AR19"/>
-      <x:c r="AS19"/>
-      <x:c r="AT19"/>
       <x:c r="AU19"/>
       <x:c r="AV19"/>
       <x:c r="AW19"/>
       <x:c r="AX19"/>
-      <x:c r="AY19" t="n">
+      <x:c r="AY19"/>
+      <x:c r="AZ19"/>
+      <x:c r="BA19"/>
+      <x:c r="BB19"/>
+      <x:c r="BC19" t="n">
         <x:v>0.6674860908</x:v>
       </x:c>
-      <x:c r="AZ19" t="n">
+      <x:c r="BD19" t="n">
         <x:v>0.02930006059</x:v>
       </x:c>
-      <x:c r="BA19" t="n">
-        <x:v>0.7125380877</x:v>
-      </x:c>
-      <x:c r="BB19" t="n">
-        <x:v>0.01178997492</x:v>
-      </x:c>
-      <x:c r="BC19" t="n">
+      <x:c r="BE19" t="n">
         <x:v>0.1008991009</x:v>
       </x:c>
-      <x:c r="BD19" t="n">
+      <x:c r="BF19" t="n">
         <x:v>0.01251744664</x:v>
-      </x:c>
-      <x:c r="BE19" t="n">
-        <x:v>0.7429121934</x:v>
-      </x:c>
-      <x:c r="BF19" t="n">
-        <x:v>0.00356150143</x:v>
       </x:c>
       <x:c r="BG19" t="n">
         <x:v>0.0831676607</x:v>
@@ -47598,30 +47071,6 @@
       <x:c r="BQ19"/>
       <x:c r="BR19" t="str">
         <x:v>active_pixel_count;bbox_fill_ratio;ToT_density;ToA_span;ToA_major_axis_corr_abs</x:v>
-      </x:c>
-      <x:c r="BS19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BT19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BU19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BV19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BW19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BX19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BY19" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="BZ19" t="n">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
